--- a/src/main/resources/Program_Field_Values_Yes.xlsx
+++ b/src/main/resources/Program_Field_Values_Yes.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500C8C68-1975-4E7D-B692-1551A451065B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3490C6-6887-4EFB-9BEC-C5A256A589E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StaticRecordProgramCreation" sheetId="39" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="149">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -401,6 +401,9 @@
     <t>Automation Direct Grant</t>
   </si>
   <si>
+    <t>Automation Program For Test</t>
+  </si>
+  <si>
     <t>Automation Program For Announcement</t>
   </si>
   <si>
@@ -422,6 +425,9 @@
     <t>Program Manager</t>
   </si>
   <si>
+    <t>GMS Administrator</t>
+  </si>
+  <si>
     <t>fieldAllocationlevel__c</t>
   </si>
   <si>
@@ -477,21 +483,6 @@
   </si>
   <si>
     <t>Objectives__c</t>
-  </si>
-  <si>
-    <t>Automation Runtime Internal Program</t>
-  </si>
-  <si>
-    <t>Type__c</t>
-  </si>
-  <si>
-    <t>PrimaryFundingOrganization__c</t>
-  </si>
-  <si>
-    <t>Test Automation Organization</t>
-  </si>
-  <si>
-    <t>FocusAreaRequired__c</t>
   </si>
   <si>
     <t>Yes</t>
@@ -557,7 +548,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -574,12 +565,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1289,7 +1274,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C5">
         <v>300</v>
@@ -1395,7 +1380,7 @@
         <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1539,10 +1524,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -1550,10 +1535,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1954,7 +1939,7 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2042,10 +2027,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2053,10 +2038,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2064,10 +2049,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2115,88 +2100,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="8" t="s">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>146</v>
+      <c r="C2" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8" t="s">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" t="s">
         <v>148</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>151</v>
-      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>151</v>
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>151</v>
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" tooltip="https://test7-internal.my.salesforce.com/00e0b000001fm3y" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{8D7FE799-8783-40F7-87C7-3B66C044DD34}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2225,10 +2207,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2236,10 +2218,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2247,7 +2229,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2557,10 +2539,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2593,7 +2575,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -2604,10 +2586,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2626,7 +2608,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C5">
         <v>1000</v>
@@ -2637,7 +2619,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -2648,7 +2630,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -2659,7 +2641,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C8">
         <v>10000</v>

--- a/src/main/resources/Program_Field_Values_Yes.xlsx
+++ b/src/main/resources/Program_Field_Values_Yes.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3490C6-6887-4EFB-9BEC-C5A256A589E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4D56F7-49ED-45AE-B073-C8B668C7CFC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StaticRecordProgramCreation" sheetId="39" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="152">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -401,9 +401,6 @@
     <t>Automation Direct Grant</t>
   </si>
   <si>
-    <t>Automation Program For Test</t>
-  </si>
-  <si>
     <t>Automation Program For Announcement</t>
   </si>
   <si>
@@ -425,9 +422,6 @@
     <t>Program Manager</t>
   </si>
   <si>
-    <t>GMS Administrator</t>
-  </si>
-  <si>
     <t>fieldAllocationlevel__c</t>
   </si>
   <si>
@@ -486,6 +480,21 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>Automation Runtime Internal Program</t>
+  </si>
+  <si>
+    <t>Type__c</t>
+  </si>
+  <si>
+    <t>PrimaryFundingOrganization__c</t>
+  </si>
+  <si>
+    <t>Test Automation Organization</t>
+  </si>
+  <si>
+    <t>FocusAreaRequired__c</t>
   </si>
 </sst>
 </file>
@@ -1274,7 +1283,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C5">
         <v>300</v>
@@ -1380,7 +1389,7 @@
         <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1524,10 +1533,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -1535,10 +1544,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -1939,7 +1948,7 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2027,10 +2036,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2038,10 +2047,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2049,10 +2058,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2118,7 +2127,7 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2126,7 +2135,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -2137,10 +2146,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" t="s">
-        <v>128</v>
+        <v>149</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2148,10 +2157,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -2159,10 +2168,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -2170,15 +2179,18 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{E44CB79E-89DD-4403-AE63-DE14844AAE1B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2207,10 +2219,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2218,10 +2230,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2229,7 +2241,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2539,10 +2551,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2575,7 +2587,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -2586,10 +2598,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2608,7 +2620,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C5">
         <v>1000</v>
@@ -2619,7 +2631,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -2630,7 +2642,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -2641,7 +2653,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C8">
         <v>10000</v>
